--- a/hourly datasets/cap_gen_year3final.xlsx
+++ b/hourly datasets/cap_gen_year3final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1053200318617804</v>
+        <v>0.1026228359312625</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06502862335842799</v>
+        <v>0.05957117952245931</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1703486552202084</v>
+        <v>0.1621940154537218</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05777295219089382</v>
+        <v>0.05174595026672387</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1630929840526742</v>
+        <v>0.1543687861979864</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04003746439820822</v>
+        <v>0.03290426805764735</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005433154263989929</v>
+        <v>0.003777400787870155</v>
       </c>
       <c r="D5" t="n">
-        <v>6.903545396162682</v>
+        <v>6.85374331434994</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07162190113110609</v>
+        <v>0.06166253452481795</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02933344314718372</v>
+        <v>0.02548456113134766</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05074148564923312</v>
+        <v>0.04032397498394789</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1453574962599886</v>
+        <v>0.1355271039889099</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +559,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02668104829557686</v>
+        <v>0.01753597748788063</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004452646875450709</v>
+        <v>0.002709443932440284</v>
       </c>
       <c r="D6" t="n">
-        <v>2.87173876220049</v>
+        <v>2.630496779893935</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03367168509957227</v>
+        <v>0.02150118017236146</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01790843688379194</v>
+        <v>0.01221993374373459</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0354536597073619</v>
+        <v>0.02285202123202665</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1320010801573573</v>
+        <v>0.1201588134191432</v>
       </c>
     </row>
     <row r="7">
@@ -587,15 +587,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01905425749260545</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+        <v>0.009617443752794384</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.00198354292450286</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.26458489246206</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.009808754045980918</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005728211183010498</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01350667632257817</v>
+      </c>
       <c r="H7" t="n">
-        <v>0.1243742893543858</v>
+        <v>0.1122402796840569</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +615,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01736560068711328</v>
+        <v>0.005797312946414095</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004163947991993477</v>
+        <v>0.001683207527650766</v>
       </c>
       <c r="D8" t="n">
-        <v>1.466885868502567</v>
+        <v>1.079624338764525</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0172446340642596</v>
+        <v>0.008607660020211337</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009142926149439599</v>
+        <v>0.002496220498510742</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02558827522478653</v>
+        <v>0.009098405394317459</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1226856325488937</v>
+        <v>0.1084201488776766</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +643,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01732275822753888</v>
+        <v>0.005366719541006251</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003113653236048236</v>
+        <v>0.001375990167125323</v>
       </c>
       <c r="D9" t="n">
-        <v>1.610124797313698</v>
+        <v>1.15391648176686</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0159669773847593</v>
+        <v>0.005589356789536984</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01120881527836379</v>
+        <v>0.002668630375832729</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02343670117671362</v>
+        <v>0.008064808706179817</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1226427900893193</v>
+        <v>0.1079895554722688</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +671,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0162799505771167</v>
+        <v>0.006598255433560738</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003428943804904028</v>
+        <v>0.001888447690366812</v>
       </c>
       <c r="D10" t="n">
-        <v>1.562044403543934</v>
+        <v>1.176892128723715</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01730849734998471</v>
+        <v>0.007896855539245101</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009556342929723413</v>
+        <v>0.002894969624225296</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02300355822450985</v>
+        <v>0.01030154124289627</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1215999824388971</v>
+        <v>0.1092210913648233</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +699,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02862222822824241</v>
+        <v>0.027506850885263</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +707,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1339422600900228</v>
+        <v>0.1301296868165255</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +717,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04430108711942315</v>
+        <v>0.04214333523486265</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +725,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1496211189812035</v>
+        <v>0.1447661711661252</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +735,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05520838535795865</v>
+        <v>0.05295987099028138</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +743,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.160528417219739</v>
+        <v>0.1555827069215439</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.06313946483995493</v>
+        <v>0.05962477511481416</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +761,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1684594967017353</v>
+        <v>0.1622476110460767</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +771,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06534465239163116</v>
+        <v>0.06165305254554034</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +779,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1706646842534116</v>
+        <v>0.1642758884768029</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +789,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06948924553581119</v>
+        <v>0.06549719830038542</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +797,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1748092773975916</v>
+        <v>0.168120034231648</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +807,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.07183312015261908</v>
+        <v>0.06893969010348656</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +815,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1771531520143995</v>
+        <v>0.1715625260347491</v>
       </c>
     </row>
     <row r="18">
@@ -815,13 +825,23 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1053200318617804</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+        <v>-0.1026228359312625</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.01009256258528256</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-17.87909037484233</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0298237897516223</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.1224590899240027</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.08278658193852285</v>
+      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -833,7 +853,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07568799403071995</v>
+        <v>0.07236019185503735</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +861,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1810080258925003</v>
+        <v>0.1749830277862999</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +871,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.07696599933625284</v>
+        <v>0.07407684298905787</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +879,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1822860311980332</v>
+        <v>0.1766996789203204</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +889,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.07958835759029037</v>
+        <v>0.07674378804402714</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +897,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1849083894520708</v>
+        <v>0.1793666239752897</v>
       </c>
     </row>
     <row r="22">
@@ -887,25 +907,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.08066186028953697</v>
+        <v>0.0780417245661825</v>
       </c>
       <c r="C22" t="n">
-        <v>0.009749602774917389</v>
+        <v>0.0091907109135273</v>
       </c>
       <c r="D22" t="n">
-        <v>14.9528240895545</v>
+        <v>14.77576145015525</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05442039328382266</v>
+        <v>0.0530269298049495</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06149311110204266</v>
+        <v>0.0599642234045948</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0998306094770315</v>
+        <v>0.09611922572777025</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1859818921513174</v>
+        <v>0.180664560497445</v>
       </c>
     </row>
     <row r="23">
@@ -915,7 +935,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.08147063306007334</v>
+        <v>0.07781820868000028</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -923,7 +943,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.1867906649218537</v>
+        <v>0.1804410446112628</v>
       </c>
     </row>
     <row r="24">
@@ -933,25 +953,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.07791512637333038</v>
+        <v>0.07529627223364527</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009884813500305314</v>
+        <v>0.009296417303914091</v>
       </c>
       <c r="D24" t="n">
-        <v>12.73343963955979</v>
+        <v>12.62596787231175</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05946162548731106</v>
+        <v>0.05708737326863336</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05848277880592048</v>
+        <v>0.057016967418575</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09734747394074011</v>
+        <v>0.09357557704871559</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1832351582351108</v>
+        <v>0.1779191081649078</v>
       </c>
     </row>
     <row r="25">
@@ -961,25 +981,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.07538410366498602</v>
+        <v>0.07085894132079737</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01044901290117689</v>
+        <v>0.009498368016295852</v>
       </c>
       <c r="D25" t="n">
-        <v>10.92792185528193</v>
+        <v>10.70526600293184</v>
       </c>
       <c r="E25" t="n">
-        <v>0.08118253572269221</v>
+        <v>0.07683758841795089</v>
       </c>
       <c r="F25" t="n">
-        <v>0.054797339215146</v>
+        <v>0.05216769687935485</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09597086811482593</v>
+        <v>0.08955018576223944</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1807041355267664</v>
+        <v>0.1734817772520599</v>
       </c>
     </row>
     <row r="26">
@@ -989,25 +1009,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.07672912400592764</v>
+        <v>0.07183177309221953</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0095112734571934</v>
+        <v>0.008724581091117819</v>
       </c>
       <c r="D26" t="n">
-        <v>-615458881264.1466</v>
+        <v>-607520685763.4102</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06873298698064179</v>
+        <v>0.06436185259195128</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05802678591276553</v>
+        <v>0.05467002685029208</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09543146209908965</v>
+        <v>0.08899351933414666</v>
       </c>
       <c r="H26" t="n">
-        <v>0.182049155867708</v>
+        <v>0.174454609023482</v>
       </c>
     </row>
     <row r="27">
@@ -1017,25 +1037,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.07461329212130874</v>
+        <v>0.06910907484016218</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009471946968351869</v>
+        <v>0.008714439401836131</v>
       </c>
       <c r="D27" t="n">
-        <v>10.08078913534554</v>
+        <v>9.995583225275162</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07725968827376228</v>
+        <v>0.07145679545043183</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05597423592445557</v>
+        <v>0.05196585286415679</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09325234831816163</v>
+        <v>0.08625229681616721</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1799333239830891</v>
+        <v>0.1717319107714247</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1065,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0716448291081884</v>
+        <v>0.06657577425057216</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00929386048126217</v>
+        <v>0.00827426838936648</v>
       </c>
       <c r="D28" t="n">
-        <v>9.783011301333788</v>
+        <v>9.726803820709135</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1032664667766986</v>
+        <v>0.09865263989622119</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05334753270758397</v>
+        <v>0.05030596517691644</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08994212550879278</v>
+        <v>0.08284558332422814</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1769648609699688</v>
+        <v>0.1691986101818347</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1093,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01837697764680676</v>
+        <v>0.008345962363854346</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003372328061941301</v>
+        <v>0.001168509330559929</v>
       </c>
       <c r="D29" t="n">
-        <v>1.910192479225142</v>
+        <v>1.300806982068285</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01332468734440235</v>
+        <v>0.004740797641788477</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01172144556022861</v>
+        <v>0.006054744946776289</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02503250973338464</v>
+        <v>0.01063717978093238</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1236970095085872</v>
+        <v>0.1109687982951169</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year3final.xlsx
+++ b/hourly datasets/cap_gen_year3final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2160700052488931</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1026228359312625</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09496018521567207</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05957117952245931</v>
+        <v>0.3370114005548073</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1621940154537218</v>
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2159015805215863</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05174595026672387</v>
+        <v>0.3435025506582138</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1543687861979864</v>
+        <v>9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2223927306249927</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +545,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03290426805764735</v>
+        <v>0.3490992267778032</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003777400787870155</v>
+        <v>0.00511712353318027</v>
       </c>
       <c r="D5" t="n">
-        <v>6.85374331434994</v>
+        <v>9.976602995746232</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06166253452481795</v>
+        <v>0.08000498392650779</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02548456113134766</v>
+        <v>0.03156840451140852</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04032397498394789</v>
+        <v>0.05166818174989633</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1355271039889099</v>
+        <v>13</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2279894067445821</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +576,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01753597748788063</v>
+        <v>0.31954221068366</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002709443932440284</v>
+        <v>0.005021295020489153</v>
       </c>
       <c r="D6" t="n">
-        <v>2.630496779893935</v>
+        <v>5.092922587829937</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02150118017236146</v>
+        <v>0.03830476852709741</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01221993374373459</v>
+        <v>0.01865467993992467</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02285202123202665</v>
+        <v>0.03835461996800122</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1201588134191432</v>
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1984323906504389</v>
       </c>
     </row>
     <row r="7">
@@ -587,25 +607,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009617443752794384</v>
+        <v>0.3068462718720736</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00198354292450286</v>
+        <v>0.004503241067662952</v>
       </c>
       <c r="D7" t="n">
-        <v>1.26458489246206</v>
+        <v>3.87325378277037</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009808754045980918</v>
+        <v>0.01095113140840081</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005728211183010498</v>
+        <v>0.009575109418742962</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01350667632257817</v>
+        <v>0.02723388898380754</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1122402796840569</v>
+        <v>15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1857364518388525</v>
       </c>
     </row>
     <row r="8">
@@ -615,25 +638,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005797312946414095</v>
+        <v>0.3069816007784952</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001683207527650766</v>
+        <v>0.004173233485417787</v>
       </c>
       <c r="D8" t="n">
-        <v>1.079624338764525</v>
+        <v>4.148291661242355</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008607660020211337</v>
+        <v>0.009059407091292639</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002496220498510742</v>
+        <v>0.007058974429432412</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009098405394317459</v>
+        <v>0.02342517730025679</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1084201488776766</v>
+        <v>15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1858717807452741</v>
       </c>
     </row>
     <row r="9">
@@ -643,25 +669,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005366719541006251</v>
+        <v>0.3092346541361226</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001375990167125323</v>
+        <v>0.0039359485807808</v>
       </c>
       <c r="D9" t="n">
-        <v>1.15391648176686</v>
+        <v>4.705211463962874</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005589356789536984</v>
+        <v>0.005799706326973911</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002668630375832729</v>
+        <v>0.008757154785013318</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008064808706179817</v>
+        <v>0.02419154948540623</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1079895554722688</v>
+        <v>15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1881248341029015</v>
       </c>
     </row>
     <row r="10">
@@ -671,25 +700,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.006598255433560738</v>
+        <v>0.3153921080474708</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001888447690366812</v>
+        <v>0.004659335003839454</v>
       </c>
       <c r="D10" t="n">
-        <v>1.176892128723715</v>
+        <v>5.583963598057381</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007896855539245101</v>
+        <v>0.009932065083657021</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002894969624225296</v>
+        <v>0.01045201986461156</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01030154124289627</v>
+        <v>0.02872513208727172</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1092210913648233</v>
+        <v>15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1942822880142497</v>
       </c>
     </row>
     <row r="11">
@@ -699,7 +731,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.027506850885263</v>
+        <v>0.2561450950057293</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -707,7 +739,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1301296868165255</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1350352749725082</v>
       </c>
     </row>
     <row r="12">
@@ -717,7 +752,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04214333523486265</v>
+        <v>0.2791475626546942</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -725,7 +760,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1447661711661252</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1580377426214731</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +773,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05295987099028138</v>
+        <v>0.2914509068748525</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -743,7 +781,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1555827069215439</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1703410868416315</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +794,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05962477511481416</v>
+        <v>0.2985054512454934</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -761,7 +802,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1622476110460767</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1773956312122723</v>
       </c>
     </row>
     <row r="15">
@@ -771,7 +815,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06165305254554034</v>
+        <v>0.302949028064648</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -779,7 +823,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1642758884768029</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1818392080314269</v>
       </c>
     </row>
     <row r="16">
@@ -789,7 +836,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06549719830038542</v>
+        <v>0.308383137333631</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -797,7 +844,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.168120034231648</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.18727331730041</v>
       </c>
     </row>
     <row r="17">
@@ -807,7 +857,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06893969010348656</v>
+        <v>0.3117970380433362</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -815,7 +865,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1715625260347491</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1906872180101152</v>
       </c>
     </row>
     <row r="18">
@@ -825,24 +878,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1026228359312625</v>
+        <v>0.1211098200332211</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01009256258528256</v>
+        <v>0.009899871293651379</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.87909037484233</v>
+        <v>-17.66044105492546</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0298237897516223</v>
+        <v>0.02862414466388264</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1224590899240027</v>
+        <v>-0.1200890225316005</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08278658193852285</v>
+        <v>-0.08117329901787994</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -853,7 +909,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.07236019185503735</v>
+        <v>0.3166092077548743</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -861,7 +917,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1749830277862999</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1954993877216533</v>
       </c>
     </row>
     <row r="20">
@@ -871,7 +930,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.07407684298905787</v>
+        <v>0.3178215844843578</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -879,7 +938,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1766996789203204</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1967117644511368</v>
       </c>
     </row>
     <row r="21">
@@ -889,7 +951,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.07674378804402714</v>
+        <v>0.3182439028188931</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -897,7 +959,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1793666239752897</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.197134082785672</v>
       </c>
     </row>
     <row r="22">
@@ -907,25 +972,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0780417245661825</v>
+        <v>0.3215254336445318</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0091907109135273</v>
+        <v>0.00912756723392282</v>
       </c>
       <c r="D22" t="n">
-        <v>14.77576145015525</v>
+        <v>14.74774290749303</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0530269298049495</v>
+        <v>0.05265541443857727</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0599642234045948</v>
+        <v>0.05979017888990725</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09611922572777025</v>
+        <v>0.09569707610791316</v>
       </c>
       <c r="H22" t="n">
-        <v>0.180664560497445</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2004156136113108</v>
       </c>
     </row>
     <row r="23">
@@ -935,7 +1003,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.07781820868000028</v>
+        <v>0.3229327307236877</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -943,7 +1011,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.1804410446112628</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2018229106904666</v>
       </c>
     </row>
     <row r="24">
@@ -953,25 +1024,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.07529627223364527</v>
+        <v>0.3252054566003269</v>
       </c>
       <c r="C24" t="n">
-        <v>0.009296417303914091</v>
+        <v>0.009205023761777516</v>
       </c>
       <c r="D24" t="n">
-        <v>12.62596787231175</v>
+        <v>12.5779066251168</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05708737326863336</v>
+        <v>0.05663526116636238</v>
       </c>
       <c r="F24" t="n">
-        <v>0.057016967418575</v>
+        <v>0.05663350398846968</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09357557704871559</v>
+        <v>0.09283286408011859</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1779191081649078</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2040956365671058</v>
       </c>
     </row>
     <row r="25">
@@ -981,25 +1055,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.07085894132079737</v>
+        <v>0.3256450035165647</v>
       </c>
       <c r="C25" t="n">
-        <v>0.009498368016295852</v>
+        <v>0.009414967034501311</v>
       </c>
       <c r="D25" t="n">
-        <v>10.70526600293184</v>
+        <v>10.66069907269903</v>
       </c>
       <c r="E25" t="n">
-        <v>0.07683758841795089</v>
+        <v>0.07613614194118068</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05216769687935485</v>
+        <v>0.05180633009013214</v>
       </c>
       <c r="G25" t="n">
-        <v>0.08955018576223944</v>
+        <v>0.08886091053877579</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1734817772520599</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2045351834833436</v>
       </c>
     </row>
     <row r="26">
@@ -1009,25 +1086,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.07183177309221953</v>
+        <v>0.3279961251147782</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008724581091117819</v>
+        <v>0.008635688019333433</v>
       </c>
       <c r="D26" t="n">
-        <v>-607520685763.4102</v>
+        <v>-607448815671.7063</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06436185259195128</v>
+        <v>0.06364407058058456</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05467002685029208</v>
+        <v>0.05408182935324821</v>
       </c>
       <c r="G26" t="n">
-        <v>0.08899351933414666</v>
+        <v>0.08805591125974711</v>
       </c>
       <c r="H26" t="n">
-        <v>0.174454609023482</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2068863050815571</v>
       </c>
     </row>
     <row r="27">
@@ -1037,25 +1117,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.06910907484016218</v>
+        <v>0.3303336893252045</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008714439401836131</v>
+        <v>0.008604519413530701</v>
       </c>
       <c r="D27" t="n">
-        <v>9.995583225275162</v>
+        <v>9.92613109719851</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07145679545043183</v>
+        <v>0.07047485905999704</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05196585286415679</v>
+        <v>0.05137004090429417</v>
       </c>
       <c r="G27" t="n">
-        <v>0.08625229681616721</v>
+        <v>0.08522454670799964</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1717319107714247</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2092238692919834</v>
       </c>
     </row>
     <row r="28">
@@ -1065,25 +1148,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.06657577425057216</v>
+        <v>0.3282171640167969</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00827426838936648</v>
+        <v>0.008146246676459318</v>
       </c>
       <c r="D28" t="n">
-        <v>9.726803820709135</v>
+        <v>9.595139785821809</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09865263989622119</v>
+        <v>0.09754872910295366</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05030596517691644</v>
+        <v>0.04938691440010114</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08284558332422814</v>
+        <v>0.08142334857724108</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1691986101818347</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2071073439835758</v>
       </c>
     </row>
     <row r="29">
@@ -1093,25 +1179,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.008345962363854346</v>
+        <v>0.3178081739994645</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001168509330559929</v>
+        <v>0.003604850760643834</v>
       </c>
       <c r="D29" t="n">
-        <v>1.300806982068285</v>
+        <v>5.77840738824491</v>
       </c>
       <c r="E29" t="n">
-        <v>0.004740797641788477</v>
+        <v>0.00491689980963269</v>
       </c>
       <c r="F29" t="n">
-        <v>0.006054744946776289</v>
+        <v>0.01605148455483677</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01063717978093238</v>
+        <v>0.03018750631207594</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1109687982951169</v>
+        <v>15</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1966983539662434</v>
       </c>
     </row>
   </sheetData>
